--- a/data/typology_templates/08_LAQ.xlsx
+++ b/data/typology_templates/08_LAQ.xlsx
@@ -425,13 +425,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:Y2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
@@ -467,110 +467,115 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Unit/Theme</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Chapter No._Name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>S.No.</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Competency</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Learning Outcome</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Blooms Taxonomy</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Explanation of Blooms Taxonomy</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Typology</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Question Image</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Option 1</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Option 2</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Option 3</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Option 4</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Image 1</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Image 2</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Image 3</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Image 4</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Answer</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Answer Image</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Explanation/Remarks</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Marks</t>
         </is>
@@ -587,57 +592,62 @@
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Book 1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>CH-1: Finding the Furry Cat! (Pre-number Concepts)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Identifies and extends simple patterns in their surroundings, shapes and numbers</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Fills in missing elements of simple, repeating patterns in different aspects (for example, red, blue, red, blue, red) with others help</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Remembering</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Long Answer Question</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Explain how you count a set of objects in groups of 2s. Give one example.</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>4.png</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Make pairs of objects, then count each pair as two. Example: 5 pairs of socks = 2,4,6,8,10, so 10 socks.</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>Model answer / marking key points.</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
